--- a/excel-files/QUEZON CITY/MANUEL L. QUEZON ELEMENTRY SCHOOL.xlsx
+++ b/excel-files/QUEZON CITY/MANUEL L. QUEZON ELEMENTRY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB36F9F2-06DC-4B4C-A2D4-73768C29E528}"/>
+  <xr:revisionPtr revIDLastSave="209" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC01B7F8-3DE5-4495-BDE2-F49234E6C1AA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -67,6 +67,9 @@
     <t>Reading and Literacy</t>
   </si>
   <si>
+    <t>RO</t>
+  </si>
+  <si>
     <t>Language</t>
   </si>
   <si>
@@ -77,6 +80,9 @@
   </si>
   <si>
     <t>Math</t>
+  </si>
+  <si>
+    <t>CO</t>
   </si>
   <si>
     <t>Science</t>
@@ -98,42 +104,6 @@
   </si>
   <si>
     <t>Music and Arts</t>
-  </si>
-  <si>
-    <t>VE</t>
-  </si>
-  <si>
-    <t>TLE</t>
-  </si>
-  <si>
-    <t>AP</t>
-  </si>
-  <si>
-    <t>SHS</t>
-  </si>
-  <si>
-    <t>Personal Development</t>
-  </si>
-  <si>
-    <t>HOPE 1 and 2</t>
-  </si>
-  <si>
-    <t>HOPE 3 and 4</t>
-  </si>
-  <si>
-    <t>Physical Science</t>
-  </si>
-  <si>
-    <t>Contemporary Philippine Arts</t>
-  </si>
-  <si>
-    <t>General Mathematics</t>
-  </si>
-  <si>
-    <t>Media and Information Literacy</t>
-  </si>
-  <si>
-    <t>Statistics and Probability</t>
   </si>
   <si>
     <t>QUARTER 1</t>
@@ -308,6 +278,42 @@
   </si>
   <si>
     <t>Arts</t>
+  </si>
+  <si>
+    <t>VE</t>
+  </si>
+  <si>
+    <t>TLE</t>
+  </si>
+  <si>
+    <t>AP</t>
+  </si>
+  <si>
+    <t>SHS</t>
+  </si>
+  <si>
+    <t>Personal Development</t>
+  </si>
+  <si>
+    <t>HOPE 1 and 2</t>
+  </si>
+  <si>
+    <t>HOPE 3 and 4</t>
+  </si>
+  <si>
+    <t>Physical Science</t>
+  </si>
+  <si>
+    <t>Contemporary Philippine Arts</t>
+  </si>
+  <si>
+    <t>General Mathematics</t>
+  </si>
+  <si>
+    <t>Media and Information Literacy</t>
+  </si>
+  <si>
+    <t>Statistics and Probability</t>
   </si>
 </sst>
 </file>
@@ -496,7 +502,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -588,30 +594,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right/>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -625,7 +607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -703,15 +685,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -727,13 +700,19 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -747,12 +726,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3019,8 +2992,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
-  <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H49" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
+  <autoFilter ref="A1:H49" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
     <tableColumn id="2" xr3:uid="{56826189-DC15-4CA2-B5A0-8F4CEC09DDAB}" name="SUBJECTS"/>
@@ -3036,8 +3009,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
-  <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA61" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+  <autoFilter ref="A2:AA61" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
     <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="55"/>
@@ -3465,7 +3438,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H98"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.85546875" customWidth="1"/>
@@ -3508,17 +3481,25 @@
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="5"/>
+      <c r="C2" s="1">
+        <v>980</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1040</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G2" s="3">
         <f>IF((C2-D2)&lt;0,0,C2-D2)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
         <f>IF((D2-C2)&lt;0,0,D2-C2)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="29.25" customHeight="1">
@@ -3526,19 +3507,27 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
+        <v>980</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1040</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="5"/>
       <c r="G3" s="3">
         <f>IF((C3-D3)&lt;0,0,C3-D3)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
         <f>IF((D3-C3)&lt;0,0,D3-C3)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21" customHeight="1">
@@ -3546,19 +3535,27 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="5"/>
+        <v>11</v>
+      </c>
+      <c r="C4" s="1">
+        <v>980</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1040</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G4" s="3">
         <f>IF((C4-D4)&lt;0,0,C4-D4)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
         <f>IF((D4-C4)&lt;0,0,D4-C4)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25.5" customHeight="1">
@@ -3566,35 +3563,45 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="C5" s="1">
+        <v>980</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1040</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G5" s="3">
         <f t="shared" ref="G5:G6" si="0">IF((C5-D5)&lt;0,0,C5-D5)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" ref="H5:H6" si="1">IF((D5-C5)&lt;0,0,D5-C5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="19.149999999999999">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C6" s="1">
+        <v>980</v>
+      </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="5"/>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="1"/>
@@ -3613,13 +3620,15 @@
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1">
+        <v>1050</v>
+      </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="5"/>
       <c r="G8" s="3">
         <f>IF((C8-D8)&lt;0,0,C8-D8)</f>
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="H8" s="4">
         <f>IF((D8-C8)&lt;0,0,D8-C8)</f>
@@ -3631,15 +3640,17 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1050</v>
+      </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="5"/>
       <c r="G9" s="3">
         <f>IF((C9-D9)&lt;0,0,C9-D9)</f>
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="H9" s="4">
         <f>IF((D9-C9)&lt;0,0,D9-C9)</f>
@@ -3651,15 +3662,17 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1050</v>
+      </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="5"/>
       <c r="G10" s="3">
         <f>IF((C10-D10)&lt;0,0,C10-D10)</f>
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="H10" s="4">
         <f>IF((D10-C10)&lt;0,0,D10-C10)</f>
@@ -3671,12 +3684,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1050</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1050</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
         <v>0</v>
@@ -3686,20 +3707,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.149999999999999">
+    <row r="12" spans="1:8" ht="20.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1050</v>
+      </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="5"/>
       <c r="G12" s="3">
         <f>IF((C12-D12)&lt;0,0,C12-D12)</f>
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="H12" s="4">
         <f>IF((D12-C12)&lt;0,0,D12-C12)</f>
@@ -3718,13 +3741,15 @@
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1">
+        <v>1151</v>
+      </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="5"/>
       <c r="G14" s="3">
         <f t="shared" ref="G14:G19" si="2">IF((C14-D14)&lt;0,0,C14-D14)</f>
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" ref="H14:H19" si="3">IF((D14-C14)&lt;0,0,D14-C14)</f>
@@ -3736,15 +3761,17 @@
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1151</v>
+      </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="5"/>
       <c r="G15" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="3"/>
@@ -3756,15 +3783,17 @@
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1151</v>
+      </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="5"/>
       <c r="G16" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="H16" s="4">
         <f t="shared" si="3"/>
@@ -3776,15 +3805,17 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1151</v>
+      </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="5"/>
       <c r="G17" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="H17" s="4">
         <f t="shared" si="3"/>
@@ -3796,35 +3827,39 @@
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1151</v>
+      </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="5"/>
       <c r="G18" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.149999999999999">
+    <row r="19" spans="1:8" ht="20.25">
       <c r="A19" s="1">
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1151</v>
+      </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="5"/>
       <c r="G19" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="3"/>
@@ -3846,15 +3881,17 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1215</v>
+      </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="5"/>
       <c r="G21" s="3">
         <f t="shared" ref="G21:G29" si="4">IF((C21-D21)&lt;0,0,C21-D21)</f>
-        <v>0</v>
+        <v>1215</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" ref="H21:H29" si="5">IF((D21-C21)&lt;0,0,D21-C21)</f>
@@ -3866,35 +3903,51 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="5"/>
+        <v>17</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1215</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1125</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.149999999999999">
+    <row r="23" spans="1:8" ht="18">
       <c r="A23" s="1">
         <v>4</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="5"/>
+        <v>13</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1215</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1125</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="5"/>
@@ -3906,15 +3959,23 @@
         <v>4</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="5"/>
+        <v>11</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1215</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1125</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="5"/>
@@ -3926,15 +3987,23 @@
         <v>4</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1215</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1125</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="5"/>
@@ -3946,15 +4015,23 @@
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1215</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1125</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" si="5"/>
@@ -3966,15 +4043,23 @@
         <v>4</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="5"/>
+        <v>19</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1215</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1125</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" si="5"/>
@@ -3986,15 +4071,17 @@
         <v>4</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1215</v>
+      </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="5"/>
       <c r="G28" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1215</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="5"/>
@@ -4006,15 +4093,23 @@
         <v>4</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1215</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1125</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
@@ -4036,19 +4131,27 @@
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1100</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1">
@@ -4056,15 +4159,17 @@
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1006</v>
+      </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="5"/>
       <c r="G32" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="7"/>
@@ -4076,15 +4181,17 @@
         <v>5</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1006</v>
+      </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="5"/>
       <c r="G33" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="7"/>
@@ -4096,15 +4203,17 @@
         <v>5</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1006</v>
+      </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="5"/>
       <c r="G34" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="7"/>
@@ -4116,19 +4225,27 @@
         <v>5</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="C35" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1100</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="27.75" customHeight="1">
@@ -4136,19 +4253,27 @@
         <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1100</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1">
@@ -4156,19 +4281,27 @@
         <v>5</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="5"/>
+        <v>19</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1100</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="27.75" customHeight="1">
@@ -4176,19 +4309,27 @@
         <v>5</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1100</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4196,15 +4337,17 @@
         <v>5</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1006</v>
+      </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="5"/>
       <c r="G39" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="7"/>
@@ -4226,15 +4369,17 @@
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C41" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="C41" s="1">
+        <v>992</v>
+      </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="5"/>
       <c r="G41" s="3">
         <f t="shared" ref="G41:G49" si="8">IF((C41-D41)&lt;0,0,C41-D41)</f>
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="H41" s="4">
         <f t="shared" ref="H41:H49" si="9">IF((D41-C41)&lt;0,0,D41-C41)</f>
@@ -4246,15 +4391,17 @@
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C42" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="C42" s="1">
+        <v>992</v>
+      </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="5"/>
       <c r="G42" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="H42" s="4">
         <f t="shared" si="9"/>
@@ -4266,15 +4413,17 @@
         <v>6</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C43" s="1">
+        <v>992</v>
+      </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="5"/>
       <c r="G43" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" si="9"/>
@@ -4286,15 +4435,17 @@
         <v>6</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="C44" s="1">
+        <v>992</v>
+      </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="5"/>
       <c r="G44" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" si="9"/>
@@ -4306,15 +4457,17 @@
         <v>6</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="C45" s="1">
+        <v>992</v>
+      </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="5"/>
       <c r="G45" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="H45" s="4">
         <f t="shared" si="9"/>
@@ -4326,15 +4479,17 @@
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="C46" s="1">
+        <v>992</v>
+      </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="5"/>
       <c r="G46" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="H46" s="4">
         <f t="shared" si="9"/>
@@ -4346,15 +4501,17 @@
         <v>6</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C47" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="C47" s="1">
+        <v>992</v>
+      </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="5"/>
       <c r="G47" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="H47" s="4">
         <f t="shared" si="9"/>
@@ -4366,15 +4523,17 @@
         <v>6</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C48" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="C48" s="1">
+        <v>992</v>
+      </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="5"/>
       <c r="G48" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="H48" s="4">
         <f t="shared" si="9"/>
@@ -4386,969 +4545,87 @@
         <v>6</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="C49" s="1">
+        <v>992</v>
+      </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="5"/>
       <c r="G49" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="H49" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-    </row>
-    <row r="51" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A51" s="10">
-        <v>7</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="3">
-        <f t="shared" ref="G51:G59" si="10">IF((C51-D51)&lt;0,0,C51-D51)</f>
-        <v>0</v>
-      </c>
-      <c r="H51" s="4">
-        <f t="shared" ref="H51:H59" si="11">IF((D51-C51)&lt;0,0,D51-C51)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A52" s="10">
-        <v>7</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H52" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A53" s="10">
-        <v>7</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H53" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A54" s="10">
-        <v>7</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H54" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="39" customHeight="1">
-      <c r="A55" s="10">
-        <v>7</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H55" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A56" s="10">
-        <v>7</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H56" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A57" s="10">
-        <v>7</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H57" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A58" s="10">
-        <v>7</v>
-      </c>
-      <c r="B58" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H58" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A59" s="10">
-        <v>7</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H59" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A60" s="7"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-    </row>
-    <row r="61" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A61" s="10">
-        <v>8</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="3">
-        <f t="shared" ref="G61:G69" si="12">IF((C61-D61)&lt;0,0,C61-D61)</f>
-        <v>0</v>
-      </c>
-      <c r="H61" s="4">
-        <f t="shared" ref="H61:H69" si="13">IF((D61-C61)&lt;0,0,D61-C61)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A62" s="10">
-        <v>8</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H62" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A63" s="10">
-        <v>8</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
-      <c r="E63" s="10"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H63" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A64" s="10">
-        <v>8</v>
-      </c>
-      <c r="B64" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
-      <c r="E64" s="10"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H64" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A65" s="10">
-        <v>8</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H65" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A66" s="10">
-        <v>8</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H66" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A67" s="10">
-        <v>8</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C67" s="10"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="10"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H67" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A68" s="10">
-        <v>8</v>
-      </c>
-      <c r="B68" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="10"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H68" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A69" s="10">
-        <v>8</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C69" s="10"/>
-      <c r="D69" s="10"/>
-      <c r="E69" s="10"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H69" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A70" s="7"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-    </row>
-    <row r="71" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A71" s="10">
-        <v>9</v>
-      </c>
-      <c r="B71" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C71" s="10"/>
-      <c r="D71" s="10"/>
-      <c r="E71" s="10"/>
-      <c r="F71" s="12"/>
-      <c r="G71" s="3">
-        <f t="shared" ref="G71:G79" si="14">IF((C71-D71)&lt;0,0,C71-D71)</f>
-        <v>0</v>
-      </c>
-      <c r="H71" s="4">
-        <f t="shared" ref="H71:H79" si="15">IF((D71-C71)&lt;0,0,D71-C71)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A72" s="10">
-        <v>9</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C72" s="10"/>
-      <c r="D72" s="10"/>
-      <c r="E72" s="10"/>
-      <c r="F72" s="12"/>
-      <c r="G72" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="H72" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A73" s="10">
-        <v>9</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C73" s="10"/>
-      <c r="D73" s="10"/>
-      <c r="E73" s="10"/>
-      <c r="F73" s="12"/>
-      <c r="G73" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="H73" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A74" s="10">
-        <v>9</v>
-      </c>
-      <c r="B74" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="10"/>
-      <c r="F74" s="12"/>
-      <c r="G74" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="H74" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A75" s="10">
-        <v>9</v>
-      </c>
-      <c r="B75" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="10"/>
-      <c r="F75" s="12"/>
-      <c r="G75" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="H75" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A76" s="10">
-        <v>9</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="H76" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A77" s="10">
-        <v>9</v>
-      </c>
-      <c r="B77" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C77" s="10"/>
-      <c r="D77" s="10"/>
-      <c r="E77" s="10"/>
-      <c r="F77" s="12"/>
-      <c r="G77" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="H77" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A78" s="10">
-        <v>9</v>
-      </c>
-      <c r="B78" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="H78" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A79" s="10">
-        <v>9</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="H79" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A80" s="7"/>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-    </row>
-    <row r="81" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A81" s="10">
-        <v>10</v>
-      </c>
-      <c r="B81" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C81" s="10"/>
-      <c r="D81" s="10"/>
-      <c r="E81" s="10"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="3">
-        <f t="shared" ref="G81:G89" si="16">IF((C81-D81)&lt;0,0,C81-D81)</f>
-        <v>0</v>
-      </c>
-      <c r="H81" s="4">
-        <f t="shared" ref="H81:H89" si="17">IF((D81-C81)&lt;0,0,D81-C81)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A82" s="10">
-        <v>10</v>
-      </c>
-      <c r="B82" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C82" s="10"/>
-      <c r="D82" s="10"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="H82" s="4">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A83" s="10">
-        <v>10</v>
-      </c>
-      <c r="B83" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C83" s="10"/>
-      <c r="D83" s="10"/>
-      <c r="E83" s="10"/>
-      <c r="F83" s="12"/>
-      <c r="G83" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="H83" s="4">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A84" s="10">
-        <v>10</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C84" s="10"/>
-      <c r="D84" s="10"/>
-      <c r="E84" s="10"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="H84" s="4">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A85" s="10">
-        <v>10</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C85" s="10"/>
-      <c r="D85" s="10"/>
-      <c r="E85" s="10"/>
-      <c r="F85" s="12"/>
-      <c r="G85" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="H85" s="4">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A86" s="10">
-        <v>10</v>
-      </c>
-      <c r="B86" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C86" s="10"/>
-      <c r="D86" s="10"/>
-      <c r="E86" s="10"/>
-      <c r="F86" s="12"/>
-      <c r="G86" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="H86" s="4">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A87" s="10">
-        <v>10</v>
-      </c>
-      <c r="B87" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C87" s="10"/>
-      <c r="D87" s="10"/>
-      <c r="E87" s="10"/>
-      <c r="F87" s="12"/>
-      <c r="G87" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="H87" s="4">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A88" s="10">
-        <v>10</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C88" s="10"/>
-      <c r="D88" s="10"/>
-      <c r="E88" s="10"/>
-      <c r="F88" s="12"/>
-      <c r="G88" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="H88" s="4">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A89" s="10">
-        <v>10</v>
-      </c>
-      <c r="B89" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C89" s="10"/>
-      <c r="D89" s="10"/>
-      <c r="E89" s="10"/>
-      <c r="F89" s="12"/>
-      <c r="G89" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="H89" s="4">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A90" s="7"/>
-      <c r="B90" s="7"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="7"/>
-      <c r="G90" s="7"/>
-      <c r="H90" s="7"/>
-    </row>
-    <row r="91" spans="1:8" ht="39.75" customHeight="1">
-      <c r="A91" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="5"/>
-      <c r="G91" s="3">
-        <f t="shared" ref="G91:G98" si="18">IF((C91-D91)&lt;0,0,C91-D91)</f>
-        <v>0</v>
-      </c>
-      <c r="H91" s="4">
-        <f t="shared" ref="H91:H98" si="19">IF((D91-C91)&lt;0,0,D91-C91)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A92" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="5"/>
-      <c r="G92" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H92" s="4">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="5"/>
-      <c r="G93" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H93" s="4">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A94" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B94" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="5"/>
-      <c r="G94" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H94" s="4">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="40.5" customHeight="1">
-      <c r="A95" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B95" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="5"/>
-      <c r="G95" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H95" s="4">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" ht="38.25" customHeight="1">
-      <c r="A96" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B96" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="5"/>
-      <c r="G96" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H96" s="4">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A97" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B97" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="5"/>
-      <c r="G97" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H97" s="4">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" ht="47.25" customHeight="1">
-      <c r="A98" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B98" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="1"/>
-      <c r="F98" s="5"/>
-      <c r="G98" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H98" s="4">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
+    <row r="50" spans="1:8" ht="27.75" customHeight="1"/>
+    <row r="51" spans="1:8" ht="27.75" customHeight="1"/>
+    <row r="52" spans="1:8" ht="27.75" customHeight="1"/>
+    <row r="53" spans="1:8" ht="27.75" customHeight="1"/>
+    <row r="54" spans="1:8" ht="27.75" customHeight="1"/>
+    <row r="55" spans="1:8" ht="39" customHeight="1"/>
+    <row r="56" spans="1:8" ht="27.75" customHeight="1"/>
+    <row r="57" spans="1:8" ht="27.75" customHeight="1"/>
+    <row r="58" spans="1:8" ht="27.75" customHeight="1"/>
+    <row r="59" spans="1:8" ht="27.75" customHeight="1"/>
+    <row r="60" spans="1:8" ht="27.75" customHeight="1"/>
+    <row r="61" spans="1:8" ht="27.75" customHeight="1"/>
+    <row r="62" spans="1:8" ht="27.75" customHeight="1"/>
+    <row r="63" spans="1:8" ht="27.75" customHeight="1"/>
+    <row r="64" spans="1:8" ht="27.75" customHeight="1"/>
+    <row r="65" ht="27.75" customHeight="1"/>
+    <row r="66" ht="27.75" customHeight="1"/>
+    <row r="67" ht="27.75" customHeight="1"/>
+    <row r="68" ht="27.75" customHeight="1"/>
+    <row r="69" ht="27.75" customHeight="1"/>
+    <row r="70" ht="27.75" customHeight="1"/>
+    <row r="71" ht="27.75" customHeight="1"/>
+    <row r="72" ht="27.75" customHeight="1"/>
+    <row r="73" ht="27.75" customHeight="1"/>
+    <row r="74" ht="27.75" customHeight="1"/>
+    <row r="75" ht="27.75" customHeight="1"/>
+    <row r="76" ht="27.75" customHeight="1"/>
+    <row r="77" ht="27.75" customHeight="1"/>
+    <row r="78" ht="27.75" customHeight="1"/>
+    <row r="79" ht="27.75" customHeight="1"/>
+    <row r="80" ht="27.75" customHeight="1"/>
+    <row r="81" ht="27.75" customHeight="1"/>
+    <row r="82" ht="27.75" customHeight="1"/>
+    <row r="83" ht="27.75" customHeight="1"/>
+    <row r="84" ht="27.75" customHeight="1"/>
+    <row r="85" ht="27.75" customHeight="1"/>
+    <row r="86" ht="27.75" customHeight="1"/>
+    <row r="87" ht="27.75" customHeight="1"/>
+    <row r="88" ht="27.75" customHeight="1"/>
+    <row r="89" ht="27.75" customHeight="1"/>
+    <row r="90" ht="27.75" customHeight="1"/>
+    <row r="91" ht="39.75" customHeight="1"/>
+    <row r="92" ht="27.75" customHeight="1"/>
+    <row r="93" ht="27.75" customHeight="1"/>
+    <row r="94" ht="27.75" customHeight="1"/>
+    <row r="95" ht="40.5" customHeight="1"/>
+    <row r="96" ht="38.25" customHeight="1"/>
+    <row r="97" ht="27.75" customHeight="1"/>
+    <row r="98" ht="47.25" customHeight="1"/>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C1:E98" name="Textbooks"/>
-    <protectedRange sqref="F1:F98" name="SOURCE"/>
+    <protectedRange sqref="C1:E49" name="Textbooks"/>
+    <protectedRange sqref="F1:F49" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:E12 E14:E19 E21:E29 E31:E39 E41:E49" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F41:F49 F2:F6 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6" xr:uid="{5F2065F9-F069-45D0-AE2D-FE27AB6815E8}">
       <formula1>"2024,2025,2026"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{6F2F3566-4D40-4EFE-A73F-949AA7C7C044}">
-      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5360,8 +4637,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA127"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <dimension ref="A1:AA111"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
     <col min="2" max="2" width="27.85546875" customWidth="1"/>
@@ -5390,38 +4667,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="D1" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="W1" s="42"/>
+      <c r="X1" s="42"/>
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="42"/>
+      <c r="AA1" s="42"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5434,106 +4711,106 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="O2" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="P2" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="Q2" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="R2" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="S2" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="T2" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="U2" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="V2" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="W2" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="X2" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="Y2" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="Z2" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="Q2" s="24" t="s">
+      <c r="AA2" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="R2" s="25" t="s">
+    </row>
+    <row r="3" spans="1:27" ht="30.6" customHeight="1">
+      <c r="A3" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="S2" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="T2" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="U2" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="V2" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="W2" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="X2" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y2" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z2" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA2" s="26" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="30.6" customHeight="1">
-      <c r="A3" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="34">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34">
+      <c r="B3" s="30"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="31">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31">
         <f>IF((D3-E3)&lt;0,0,(D3-E3))</f>
         <v>0</v>
       </c>
-      <c r="I3" s="34">
+      <c r="I3" s="31">
         <f>IF((E3-D3)&lt;0,0,(E3-D3))</f>
         <v>0</v>
       </c>
-      <c r="J3" s="34">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="34"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="34"/>
+      <c r="J3" s="31">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="31"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="31"/>
       <c r="N3" s="5">
         <f t="shared" ref="N3" si="0">IF((J3-K3)&lt;0,0,(J3-K3))</f>
         <v>0</v>
@@ -5546,34 +4823,34 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="34"/>
-      <c r="R3" s="32"/>
-      <c r="S3" s="34"/>
-      <c r="T3" s="34">
+      <c r="Q3" s="31"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31">
         <f>IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
         <v>0</v>
       </c>
-      <c r="U3" s="34">
+      <c r="U3" s="31">
         <f>IF((Q3-P3)&lt;0,0,(Q3-P3))</f>
         <v>0</v>
       </c>
-      <c r="V3" s="34">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W3" s="34"/>
-      <c r="X3" s="32"/>
-      <c r="Y3" s="34"/>
-      <c r="Z3" s="34">
+      <c r="V3" s="31">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W3" s="31"/>
+      <c r="X3" s="29"/>
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31">
         <f>IF((V3-W3)&lt;0,0,(V3-W3))</f>
         <v>0</v>
       </c>
-      <c r="AA3" s="34">
+      <c r="AA3" s="31">
         <f>IF((W3-V3)&lt;0,0,(W3-V3))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -5585,7 +4862,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="34.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5601,11 +4878,11 @@
       <c r="F5" s="1"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
-        <f t="shared" ref="H5:H77" si="2">IF((D5-E5)&lt;0,0,(D5-E5))</f>
+        <f t="shared" ref="H5:H61" si="2">IF((D5-E5)&lt;0,0,(D5-E5))</f>
         <v>0</v>
       </c>
       <c r="I5" s="5">
-        <f t="shared" ref="I5:I77" si="3">IF((E5-D5)&lt;0,0,(E5-D5))</f>
+        <f t="shared" ref="I5:I61" si="3">IF((E5-D5)&lt;0,0,(E5-D5))</f>
         <v>0</v>
       </c>
       <c r="J5" s="5">
@@ -5654,12 +4931,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="20.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="5">
@@ -5685,11 +4962,11 @@
       <c r="L6" s="1"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
-        <f t="shared" ref="N6:N69" si="10">IF((J6-K6)&lt;0,0,(J6-K6))</f>
+        <f t="shared" ref="N6:N61" si="10">IF((J6-K6)&lt;0,0,(J6-K6))</f>
         <v>0</v>
       </c>
       <c r="O6" s="5">
-        <f t="shared" ref="O6:O69" si="11">IF((K6-J6)&lt;0,0,(K6-J6))</f>
+        <f t="shared" ref="O6:O61" si="11">IF((K6-J6)&lt;0,0,(K6-J6))</f>
         <v>0</v>
       </c>
       <c r="P6" s="5">
@@ -5700,11 +4977,11 @@
       <c r="R6" s="1"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5">
-        <f t="shared" ref="T6:T69" si="12">IF((P6-Q6)&lt;0,0,(P6-Q6))</f>
+        <f t="shared" ref="T6:T61" si="12">IF((P6-Q6)&lt;0,0,(P6-Q6))</f>
         <v>0</v>
       </c>
       <c r="U6" s="5">
-        <f t="shared" ref="U6:U69" si="13">IF((Q6-P6)&lt;0,0,(Q6-P6))</f>
+        <f t="shared" ref="U6:U61" si="13">IF((Q6-P6)&lt;0,0,(Q6-P6))</f>
         <v>0</v>
       </c>
       <c r="V6" s="5">
@@ -5715,20 +4992,20 @@
       <c r="X6" s="1"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
-        <f t="shared" ref="Z6:Z69" si="14">IF((V6-W6)&lt;0,0,(V6-W6))</f>
+        <f t="shared" ref="Z6:Z61" si="14">IF((V6-W6)&lt;0,0,(V6-W6))</f>
         <v>0</v>
       </c>
       <c r="AA6" s="5">
-        <f t="shared" ref="AA6:AA69" si="15">IF((W6-V6)&lt;0,0,(W6-V6))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+        <f t="shared" ref="AA6:AA61" si="15">IF((W6-V6)&lt;0,0,(W6-V6))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="20.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="5">
@@ -5792,12 +5069,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="20.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -5861,12 +5138,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="20.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -5930,12 +5207,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="20.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -5999,12 +5276,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="20.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="5">
@@ -6068,12 +5345,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="20.25">
       <c r="A12" s="1">
         <v>1</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="5">
@@ -6137,7 +5414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6150,7 +5427,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="34.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6219,12 +5496,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="20.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="5">
@@ -6288,12 +5565,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="20.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="5">
@@ -6357,12 +5634,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="20.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="5">
@@ -6426,12 +5703,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="20.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="5">
@@ -6495,12 +5772,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="20.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="5">
@@ -6564,12 +5841,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="20.25">
       <c r="A20" s="1">
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="5">
@@ -6633,12 +5910,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="20.25">
       <c r="A21" s="1">
         <v>2</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="5">
@@ -6702,7 +5979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6716,7 +5993,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="34.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6785,12 +6062,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="20.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -6854,12 +6131,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="20.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="5">
@@ -6923,12 +6200,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="20.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="5">
@@ -6992,12 +6269,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="20.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="5">
@@ -7061,12 +6338,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="20.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="5">
@@ -7130,12 +6407,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="20.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="5">
@@ -7199,12 +6476,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="20.25">
       <c r="A30" s="1">
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="5">
@@ -7268,12 +6545,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="20.25">
       <c r="A31" s="1">
         <v>3</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -7337,7 +6614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7351,12 +6628,12 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="20.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -7420,12 +6697,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="20.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -7489,12 +6766,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="20.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="5">
@@ -7558,12 +6835,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="20.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -7627,12 +6904,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="20.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="5">
@@ -7696,12 +6973,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="20.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -7765,12 +7042,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="20.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="5">
@@ -7834,12 +7111,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="20.25">
       <c r="A40" s="1">
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="5">
@@ -7903,12 +7180,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="20.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -7972,7 +7249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -7986,12 +7263,12 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="20.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -8055,12 +7332,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="20.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -8124,12 +7401,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="20.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="5">
@@ -8193,12 +7470,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="20.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="5">
@@ -8262,12 +7539,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="20.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="5">
@@ -8331,12 +7608,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="20.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -8400,12 +7677,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="20.25">
       <c r="A49" s="1">
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="5">
@@ -8469,12 +7746,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="20.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -8538,12 +7815,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="20.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="5">
@@ -8607,7 +7884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8621,12 +7898,12 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="20.25">
       <c r="A53" s="1">
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -8690,12 +7967,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="20.25">
       <c r="A54" s="1">
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="5">
@@ -8759,12 +8036,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="20.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="5">
@@ -8828,12 +8105,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="20.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="5">
@@ -8897,12 +8174,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="20.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="5">
@@ -8966,12 +8243,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="20.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -9035,12 +8312,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="20.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="5">
@@ -9104,12 +8381,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="20.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="5">
@@ -9173,12 +8450,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="20.25">
       <c r="A61" s="1">
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="5">
@@ -9242,4117 +8519,185 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
-      <c r="J62" s="13"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="13"/>
-      <c r="O62" s="13"/>
-      <c r="P62" s="13"/>
-      <c r="S62" s="5"/>
-      <c r="T62" s="13"/>
-      <c r="U62" s="13"/>
-      <c r="V62" s="13"/>
-      <c r="Y62" s="5"/>
-      <c r="Z62" s="13"/>
-      <c r="AA62" s="13"/>
-    </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
-      <c r="A63" s="10">
-        <v>7</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C63" s="10"/>
-      <c r="D63" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E63" s="12"/>
-      <c r="F63" s="10"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I63" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J63" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K63" s="12"/>
-      <c r="L63" s="10"/>
-      <c r="M63" s="12"/>
-      <c r="N63" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O63" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P63" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q63" s="12"/>
-      <c r="R63" s="10"/>
-      <c r="S63" s="12"/>
-      <c r="T63" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U63" s="12">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V63" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W63" s="12"/>
-      <c r="X63" s="10"/>
-      <c r="Y63" s="12"/>
-      <c r="Z63" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA63" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
-      <c r="A64" s="10">
-        <v>7</v>
-      </c>
-      <c r="B64" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E64" s="12"/>
-      <c r="F64" s="10"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I64" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J64" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K64" s="12"/>
-      <c r="L64" s="10"/>
-      <c r="M64" s="12"/>
-      <c r="N64" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O64" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P64" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q64" s="12"/>
-      <c r="R64" s="10"/>
-      <c r="S64" s="12"/>
-      <c r="T64" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U64" s="12">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V64" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W64" s="12"/>
-      <c r="X64" s="10"/>
-      <c r="Y64" s="12"/>
-      <c r="Z64" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA64" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
-      <c r="A65" s="10">
-        <v>7</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C65" s="10"/>
-      <c r="D65" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E65" s="12"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I65" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J65" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K65" s="12"/>
-      <c r="L65" s="10"/>
-      <c r="M65" s="12"/>
-      <c r="N65" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O65" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P65" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q65" s="12"/>
-      <c r="R65" s="10"/>
-      <c r="S65" s="12"/>
-      <c r="T65" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U65" s="12">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V65" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W65" s="12"/>
-      <c r="X65" s="10"/>
-      <c r="Y65" s="12"/>
-      <c r="Z65" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA65" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
-      <c r="A66" s="10">
-        <v>7</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C66" s="10"/>
-      <c r="D66" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E66" s="12"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I66" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J66" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K66" s="12"/>
-      <c r="L66" s="10"/>
-      <c r="M66" s="12"/>
-      <c r="N66" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O66" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P66" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q66" s="12"/>
-      <c r="R66" s="10"/>
-      <c r="S66" s="12"/>
-      <c r="T66" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U66" s="12">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V66" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W66" s="12"/>
-      <c r="X66" s="10"/>
-      <c r="Y66" s="12"/>
-      <c r="Z66" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA66" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
-      <c r="A67" s="10">
-        <v>7</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" s="10"/>
-      <c r="D67" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E67" s="12"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I67" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J67" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K67" s="12"/>
-      <c r="L67" s="10"/>
-      <c r="M67" s="12"/>
-      <c r="N67" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O67" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P67" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q67" s="12"/>
-      <c r="R67" s="10"/>
-      <c r="S67" s="12"/>
-      <c r="T67" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U67" s="12">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V67" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W67" s="12"/>
-      <c r="X67" s="10"/>
-      <c r="Y67" s="12"/>
-      <c r="Z67" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA67" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
-      <c r="A68" s="10">
-        <v>7</v>
-      </c>
-      <c r="B68" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E68" s="12"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I68" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J68" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K68" s="12"/>
-      <c r="L68" s="10"/>
-      <c r="M68" s="12"/>
-      <c r="N68" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O68" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P68" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q68" s="12"/>
-      <c r="R68" s="10"/>
-      <c r="S68" s="12"/>
-      <c r="T68" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U68" s="12">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V68" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W68" s="12"/>
-      <c r="X68" s="10"/>
-      <c r="Y68" s="12"/>
-      <c r="Z68" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA68" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
-      <c r="A69" s="10">
-        <v>7</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C69" s="10"/>
-      <c r="D69" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E69" s="12"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I69" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J69" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K69" s="12"/>
-      <c r="L69" s="10"/>
-      <c r="M69" s="12"/>
-      <c r="N69" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O69" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P69" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q69" s="12"/>
-      <c r="R69" s="10"/>
-      <c r="S69" s="12"/>
-      <c r="T69" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U69" s="12">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V69" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W69" s="12"/>
-      <c r="X69" s="10"/>
-      <c r="Y69" s="12"/>
-      <c r="Z69" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA69" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
-      <c r="A70" s="10">
-        <v>7</v>
-      </c>
-      <c r="B70" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C70" s="10"/>
-      <c r="D70" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E70" s="12"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I70" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J70" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K70" s="12"/>
-      <c r="L70" s="10"/>
-      <c r="M70" s="12"/>
-      <c r="N70" s="12">
-        <f t="shared" ref="N70:N126" si="16">IF((J70-K70)&lt;0,0,(J70-K70))</f>
-        <v>0</v>
-      </c>
-      <c r="O70" s="12">
-        <f t="shared" ref="O70:O126" si="17">IF((K70-J70)&lt;0,0,(K70-J70))</f>
-        <v>0</v>
-      </c>
-      <c r="P70" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q70" s="12"/>
-      <c r="R70" s="10"/>
-      <c r="S70" s="12"/>
-      <c r="T70" s="12">
-        <f t="shared" ref="T70:T127" si="18">IF((P70-Q70)&lt;0,0,(P70-Q70))</f>
-        <v>0</v>
-      </c>
-      <c r="U70" s="12">
-        <f t="shared" ref="U70:U127" si="19">IF((Q70-P70)&lt;0,0,(Q70-P70))</f>
-        <v>0</v>
-      </c>
-      <c r="V70" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W70" s="12"/>
-      <c r="X70" s="10"/>
-      <c r="Y70" s="12"/>
-      <c r="Z70" s="12">
-        <f t="shared" ref="Z70:Z127" si="20">IF((V70-W70)&lt;0,0,(V70-W70))</f>
-        <v>0</v>
-      </c>
-      <c r="AA70" s="12">
-        <f t="shared" ref="AA70:AA127" si="21">IF((W70-V70)&lt;0,0,(W70-V70))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
-      <c r="A71" s="10">
-        <v>7</v>
-      </c>
-      <c r="B71" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C71" s="10"/>
-      <c r="D71" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E71" s="12"/>
-      <c r="F71" s="10"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I71" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J71" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K71" s="12"/>
-      <c r="L71" s="10"/>
-      <c r="M71" s="12"/>
-      <c r="N71" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O71" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P71" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q71" s="12"/>
-      <c r="R71" s="10"/>
-      <c r="S71" s="12"/>
-      <c r="T71" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U71" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V71" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W71" s="12"/>
-      <c r="X71" s="10"/>
-      <c r="Y71" s="12"/>
-      <c r="Z71" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA71" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
-      <c r="J72" s="13"/>
-      <c r="M72" s="5"/>
-      <c r="N72" s="13"/>
-      <c r="O72" s="13"/>
-      <c r="P72" s="13"/>
-      <c r="S72" s="5"/>
-      <c r="T72" s="13"/>
-      <c r="U72" s="13"/>
-      <c r="V72" s="13"/>
-      <c r="Y72" s="5"/>
-      <c r="Z72" s="13"/>
-      <c r="AA72" s="13"/>
-    </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
-      <c r="A73" s="10">
-        <v>8</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C73" s="10"/>
-      <c r="D73" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E73" s="12"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="12"/>
-      <c r="H73" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I73" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J73" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K73" s="12"/>
-      <c r="L73" s="10"/>
-      <c r="M73" s="12"/>
-      <c r="N73" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O73" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P73" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q73" s="12"/>
-      <c r="R73" s="10"/>
-      <c r="S73" s="12"/>
-      <c r="T73" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U73" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V73" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W73" s="12"/>
-      <c r="X73" s="10"/>
-      <c r="Y73" s="12"/>
-      <c r="Z73" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA73" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
-      <c r="A74" s="10">
-        <v>8</v>
-      </c>
-      <c r="B74" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C74" s="10"/>
-      <c r="D74" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E74" s="12"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="12"/>
-      <c r="H74" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I74" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J74" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K74" s="12"/>
-      <c r="L74" s="10"/>
-      <c r="M74" s="12"/>
-      <c r="N74" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O74" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P74" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q74" s="12"/>
-      <c r="R74" s="10"/>
-      <c r="S74" s="12"/>
-      <c r="T74" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U74" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V74" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W74" s="12"/>
-      <c r="X74" s="10"/>
-      <c r="Y74" s="12"/>
-      <c r="Z74" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA74" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
-      <c r="A75" s="10">
-        <v>8</v>
-      </c>
-      <c r="B75" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C75" s="10"/>
-      <c r="D75" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E75" s="12"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I75" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J75" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K75" s="12"/>
-      <c r="L75" s="10"/>
-      <c r="M75" s="12"/>
-      <c r="N75" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O75" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P75" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q75" s="12"/>
-      <c r="R75" s="10"/>
-      <c r="S75" s="12"/>
-      <c r="T75" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U75" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V75" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W75" s="12"/>
-      <c r="X75" s="10"/>
-      <c r="Y75" s="12"/>
-      <c r="Z75" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA75" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
-      <c r="A76" s="10">
-        <v>8</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E76" s="12"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="12"/>
-      <c r="H76" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I76" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J76" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K76" s="12"/>
-      <c r="L76" s="10"/>
-      <c r="M76" s="12"/>
-      <c r="N76" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O76" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P76" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q76" s="12"/>
-      <c r="R76" s="10"/>
-      <c r="S76" s="12"/>
-      <c r="T76" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U76" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V76" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W76" s="12"/>
-      <c r="X76" s="10"/>
-      <c r="Y76" s="12"/>
-      <c r="Z76" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA76" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
-      <c r="A77" s="10">
-        <v>8</v>
-      </c>
-      <c r="B77" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C77" s="10"/>
-      <c r="D77" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E77" s="12"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="12"/>
-      <c r="H77" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I77" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J77" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K77" s="12"/>
-      <c r="L77" s="10"/>
-      <c r="M77" s="12"/>
-      <c r="N77" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O77" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P77" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q77" s="12"/>
-      <c r="R77" s="10"/>
-      <c r="S77" s="12"/>
-      <c r="T77" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U77" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V77" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W77" s="12"/>
-      <c r="X77" s="10"/>
-      <c r="Y77" s="12"/>
-      <c r="Z77" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA77" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
-      <c r="A78" s="10">
-        <v>8</v>
-      </c>
-      <c r="B78" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C78" s="10"/>
-      <c r="D78" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E78" s="12"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="12"/>
-      <c r="H78" s="12">
-        <f t="shared" ref="H78:H127" si="22">IF((D78-E78)&lt;0,0,(D78-E78))</f>
-        <v>0</v>
-      </c>
-      <c r="I78" s="12">
-        <f t="shared" ref="I78:I127" si="23">IF((E78-D78)&lt;0,0,(E78-D78))</f>
-        <v>0</v>
-      </c>
-      <c r="J78" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K78" s="12"/>
-      <c r="L78" s="10"/>
-      <c r="M78" s="12"/>
-      <c r="N78" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O78" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P78" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q78" s="12"/>
-      <c r="R78" s="10"/>
-      <c r="S78" s="12"/>
-      <c r="T78" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U78" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V78" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W78" s="12"/>
-      <c r="X78" s="10"/>
-      <c r="Y78" s="12"/>
-      <c r="Z78" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA78" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
-      <c r="A79" s="10">
-        <v>8</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C79" s="10"/>
-      <c r="D79" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E79" s="12"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I79" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J79" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K79" s="12"/>
-      <c r="L79" s="10"/>
-      <c r="M79" s="12"/>
-      <c r="N79" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O79" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P79" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q79" s="12"/>
-      <c r="R79" s="10"/>
-      <c r="S79" s="12"/>
-      <c r="T79" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U79" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V79" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W79" s="12"/>
-      <c r="X79" s="10"/>
-      <c r="Y79" s="12"/>
-      <c r="Z79" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA79" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
-      <c r="A80" s="10">
-        <v>8</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C80" s="10"/>
-      <c r="D80" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E80" s="12"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="12"/>
-      <c r="H80" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I80" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J80" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K80" s="12"/>
-      <c r="L80" s="10"/>
-      <c r="M80" s="12"/>
-      <c r="N80" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O80" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P80" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q80" s="12"/>
-      <c r="R80" s="10"/>
-      <c r="S80" s="12"/>
-      <c r="T80" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U80" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V80" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W80" s="12"/>
-      <c r="X80" s="10"/>
-      <c r="Y80" s="12"/>
-      <c r="Z80" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA80" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
-      <c r="A81" s="10">
-        <v>8</v>
-      </c>
-      <c r="B81" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C81" s="10"/>
-      <c r="D81" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E81" s="12"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="12"/>
-      <c r="H81" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I81" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J81" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K81" s="12"/>
-      <c r="L81" s="10"/>
-      <c r="M81" s="12"/>
-      <c r="N81" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O81" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P81" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q81" s="12"/>
-      <c r="R81" s="10"/>
-      <c r="S81" s="12"/>
-      <c r="T81" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U81" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V81" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W81" s="12"/>
-      <c r="X81" s="10"/>
-      <c r="Y81" s="12"/>
-      <c r="Z81" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA81" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
-      <c r="J82" s="13"/>
-      <c r="M82" s="5"/>
-      <c r="N82" s="13"/>
-      <c r="O82" s="13"/>
-      <c r="P82" s="13"/>
-      <c r="S82" s="5"/>
-      <c r="T82" s="13"/>
-      <c r="U82" s="13"/>
-      <c r="V82" s="13"/>
-      <c r="Y82" s="5"/>
-      <c r="Z82" s="13"/>
-      <c r="AA82" s="13"/>
-    </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
-      <c r="A83" s="10">
-        <v>9</v>
-      </c>
-      <c r="B83" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C83" s="10"/>
-      <c r="D83" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E83" s="12"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="12"/>
-      <c r="H83" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I83" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J83" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K83" s="12"/>
-      <c r="L83" s="10"/>
-      <c r="M83" s="12"/>
-      <c r="N83" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O83" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P83" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q83" s="12"/>
-      <c r="R83" s="10"/>
-      <c r="S83" s="12"/>
-      <c r="T83" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U83" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V83" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W83" s="12"/>
-      <c r="X83" s="10"/>
-      <c r="Y83" s="12"/>
-      <c r="Z83" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA83" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
-      <c r="A84" s="10">
-        <v>9</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C84" s="10"/>
-      <c r="D84" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E84" s="12"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="12"/>
-      <c r="H84" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I84" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J84" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K84" s="12"/>
-      <c r="L84" s="10"/>
-      <c r="M84" s="12"/>
-      <c r="N84" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O84" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P84" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q84" s="12"/>
-      <c r="R84" s="10"/>
-      <c r="S84" s="12"/>
-      <c r="T84" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U84" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V84" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W84" s="12"/>
-      <c r="X84" s="10"/>
-      <c r="Y84" s="12"/>
-      <c r="Z84" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA84" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
-      <c r="A85" s="10">
-        <v>9</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C85" s="10"/>
-      <c r="D85" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E85" s="12"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="12"/>
-      <c r="H85" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I85" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J85" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K85" s="12"/>
-      <c r="L85" s="10"/>
-      <c r="M85" s="12"/>
-      <c r="N85" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O85" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P85" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q85" s="12"/>
-      <c r="R85" s="10"/>
-      <c r="S85" s="12"/>
-      <c r="T85" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U85" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V85" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W85" s="12"/>
-      <c r="X85" s="10"/>
-      <c r="Y85" s="12"/>
-      <c r="Z85" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA85" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
-      <c r="A86" s="10">
-        <v>9</v>
-      </c>
-      <c r="B86" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C86" s="10"/>
-      <c r="D86" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E86" s="12"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="12"/>
-      <c r="H86" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I86" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J86" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K86" s="12"/>
-      <c r="L86" s="10"/>
-      <c r="M86" s="12"/>
-      <c r="N86" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O86" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P86" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q86" s="12"/>
-      <c r="R86" s="10"/>
-      <c r="S86" s="12"/>
-      <c r="T86" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U86" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V86" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W86" s="12"/>
-      <c r="X86" s="10"/>
-      <c r="Y86" s="12"/>
-      <c r="Z86" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA86" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
-      <c r="A87" s="10">
-        <v>9</v>
-      </c>
-      <c r="B87" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C87" s="10"/>
-      <c r="D87" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E87" s="12"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="12"/>
-      <c r="H87" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I87" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J87" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K87" s="12"/>
-      <c r="L87" s="10"/>
-      <c r="M87" s="12"/>
-      <c r="N87" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O87" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P87" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q87" s="12"/>
-      <c r="R87" s="10"/>
-      <c r="S87" s="12"/>
-      <c r="T87" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U87" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V87" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W87" s="12"/>
-      <c r="X87" s="10"/>
-      <c r="Y87" s="12"/>
-      <c r="Z87" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA87" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
-      <c r="A88" s="10">
-        <v>9</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C88" s="10"/>
-      <c r="D88" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E88" s="12"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="12"/>
-      <c r="H88" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I88" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J88" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K88" s="12"/>
-      <c r="L88" s="10"/>
-      <c r="M88" s="12"/>
-      <c r="N88" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O88" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P88" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q88" s="12"/>
-      <c r="R88" s="10"/>
-      <c r="S88" s="12"/>
-      <c r="T88" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U88" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V88" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W88" s="12"/>
-      <c r="X88" s="10"/>
-      <c r="Y88" s="12"/>
-      <c r="Z88" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA88" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
-      <c r="A89" s="10">
-        <v>9</v>
-      </c>
-      <c r="B89" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C89" s="10"/>
-      <c r="D89" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E89" s="12"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="12"/>
-      <c r="H89" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I89" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J89" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K89" s="12"/>
-      <c r="L89" s="10"/>
-      <c r="M89" s="12"/>
-      <c r="N89" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O89" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P89" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q89" s="12"/>
-      <c r="R89" s="10"/>
-      <c r="S89" s="12"/>
-      <c r="T89" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U89" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V89" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W89" s="12"/>
-      <c r="X89" s="10"/>
-      <c r="Y89" s="12"/>
-      <c r="Z89" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA89" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
-      <c r="A90" s="10">
-        <v>9</v>
-      </c>
-      <c r="B90" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C90" s="10"/>
-      <c r="D90" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E90" s="12"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="12"/>
-      <c r="H90" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I90" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J90" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K90" s="12"/>
-      <c r="L90" s="10"/>
-      <c r="M90" s="12"/>
-      <c r="N90" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O90" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P90" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q90" s="12"/>
-      <c r="R90" s="10"/>
-      <c r="S90" s="12"/>
-      <c r="T90" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U90" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V90" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W90" s="12"/>
-      <c r="X90" s="10"/>
-      <c r="Y90" s="12"/>
-      <c r="Z90" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA90" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
-      <c r="A91" s="10">
-        <v>9</v>
-      </c>
-      <c r="B91" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C91" s="10"/>
-      <c r="D91" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E91" s="12"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="12"/>
-      <c r="H91" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I91" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J91" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K91" s="12"/>
-      <c r="L91" s="10"/>
-      <c r="M91" s="12"/>
-      <c r="N91" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O91" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P91" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q91" s="12"/>
-      <c r="R91" s="10"/>
-      <c r="S91" s="12"/>
-      <c r="T91" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U91" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V91" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W91" s="12"/>
-      <c r="X91" s="10"/>
-      <c r="Y91" s="12"/>
-      <c r="Z91" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA91" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
-      <c r="J92" s="13"/>
-      <c r="M92" s="5"/>
-      <c r="N92" s="13"/>
-      <c r="O92" s="13"/>
-      <c r="P92" s="13"/>
-      <c r="S92" s="5"/>
-      <c r="T92" s="13"/>
-      <c r="U92" s="13"/>
-      <c r="V92" s="13"/>
-      <c r="Y92" s="5"/>
-      <c r="Z92" s="13"/>
-      <c r="AA92" s="13"/>
-    </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
-      <c r="A93" s="10">
-        <v>10</v>
-      </c>
-      <c r="B93" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C93" s="10"/>
-      <c r="D93" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E93" s="12"/>
-      <c r="F93" s="10"/>
-      <c r="G93" s="12"/>
-      <c r="H93" s="12">
-        <f>IF((D93-E93)&lt;0,0,(D93-E93))</f>
-        <v>0</v>
-      </c>
-      <c r="I93" s="12">
-        <f>IF((E93-D93)&lt;0,0,(E93-D93))</f>
-        <v>0</v>
-      </c>
-      <c r="J93" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K93" s="12"/>
-      <c r="L93" s="10"/>
-      <c r="M93" s="12"/>
-      <c r="N93" s="12">
-        <f>IF((J93-K93)&lt;0,0,(J93-K93))</f>
-        <v>0</v>
-      </c>
-      <c r="O93" s="12">
-        <f>IF((K93-J93)&lt;0,0,(K93-J93))</f>
-        <v>0</v>
-      </c>
-      <c r="P93" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q93" s="12"/>
-      <c r="R93" s="10"/>
-      <c r="S93" s="12"/>
-      <c r="T93" s="12">
-        <f>IF((P93-Q93)&lt;0,0,(P93-Q93))</f>
-        <v>0</v>
-      </c>
-      <c r="U93" s="12">
-        <f>IF((Q93-P93)&lt;0,0,(Q93-P93))</f>
-        <v>0</v>
-      </c>
-      <c r="V93" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W93" s="12"/>
-      <c r="X93" s="10"/>
-      <c r="Y93" s="12"/>
-      <c r="Z93" s="12">
-        <f>IF((V93-W93)&lt;0,0,(V93-W93))</f>
-        <v>0</v>
-      </c>
-      <c r="AA93" s="12">
-        <f>IF((W93-V93)&lt;0,0,(W93-V93))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
-      <c r="A94" s="10">
-        <v>10</v>
-      </c>
-      <c r="B94" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C94" s="10"/>
-      <c r="D94" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E94" s="12"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="12"/>
-      <c r="H94" s="12">
-        <f>IF((D94-E94)&lt;0,0,(D94-E94))</f>
-        <v>0</v>
-      </c>
-      <c r="I94" s="12">
-        <f>IF((E94-D94)&lt;0,0,(E94-D94))</f>
-        <v>0</v>
-      </c>
-      <c r="J94" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K94" s="12"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="12"/>
-      <c r="N94" s="12">
-        <f>IF((J94-K94)&lt;0,0,(J94-K94))</f>
-        <v>0</v>
-      </c>
-      <c r="O94" s="12">
-        <f>IF((K94-J94)&lt;0,0,(K94-J94))</f>
-        <v>0</v>
-      </c>
-      <c r="P94" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q94" s="12"/>
-      <c r="R94" s="10"/>
-      <c r="S94" s="12"/>
-      <c r="T94" s="12">
-        <f>IF((P94-Q94)&lt;0,0,(P94-Q94))</f>
-        <v>0</v>
-      </c>
-      <c r="U94" s="12">
-        <f>IF((Q94-P94)&lt;0,0,(Q94-P94))</f>
-        <v>0</v>
-      </c>
-      <c r="V94" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W94" s="12"/>
-      <c r="X94" s="10"/>
-      <c r="Y94" s="12"/>
-      <c r="Z94" s="12">
-        <f>IF((V94-W94)&lt;0,0,(V94-W94))</f>
-        <v>0</v>
-      </c>
-      <c r="AA94" s="12">
-        <f>IF((W94-V94)&lt;0,0,(W94-V94))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
-      <c r="A95" s="10">
-        <v>10</v>
-      </c>
-      <c r="B95" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C95" s="10"/>
-      <c r="D95" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E95" s="12"/>
-      <c r="F95" s="10"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12">
-        <f>IF((D95-E95)&lt;0,0,(D95-E95))</f>
-        <v>0</v>
-      </c>
-      <c r="I95" s="12">
-        <f>IF((E95-D95)&lt;0,0,(E95-D95))</f>
-        <v>0</v>
-      </c>
-      <c r="J95" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K95" s="12"/>
-      <c r="L95" s="10"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12">
-        <f>IF((J95-K95)&lt;0,0,(J95-K95))</f>
-        <v>0</v>
-      </c>
-      <c r="O95" s="12">
-        <f>IF((K95-J95)&lt;0,0,(K95-J95))</f>
-        <v>0</v>
-      </c>
-      <c r="P95" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q95" s="12"/>
-      <c r="R95" s="10"/>
-      <c r="S95" s="12"/>
-      <c r="T95" s="12">
-        <f>IF((P95-Q95)&lt;0,0,(P95-Q95))</f>
-        <v>0</v>
-      </c>
-      <c r="U95" s="12">
-        <f>IF((Q95-P95)&lt;0,0,(Q95-P95))</f>
-        <v>0</v>
-      </c>
-      <c r="V95" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W95" s="12"/>
-      <c r="X95" s="10"/>
-      <c r="Y95" s="12"/>
-      <c r="Z95" s="12">
-        <f>IF((V95-W95)&lt;0,0,(V95-W95))</f>
-        <v>0</v>
-      </c>
-      <c r="AA95" s="12">
-        <f>IF((W95-V95)&lt;0,0,(W95-V95))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
-      <c r="A96" s="10">
-        <v>10</v>
-      </c>
-      <c r="B96" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C96" s="10"/>
-      <c r="D96" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E96" s="12"/>
-      <c r="F96" s="10"/>
-      <c r="G96" s="12"/>
-      <c r="H96" s="12">
-        <f>IF((D96-E96)&lt;0,0,(D96-E96))</f>
-        <v>0</v>
-      </c>
-      <c r="I96" s="12">
-        <f>IF((E96-D96)&lt;0,0,(E96-D96))</f>
-        <v>0</v>
-      </c>
-      <c r="J96" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K96" s="12"/>
-      <c r="L96" s="10"/>
-      <c r="M96" s="12"/>
-      <c r="N96" s="12">
-        <f>IF((J96-K96)&lt;0,0,(J96-K96))</f>
-        <v>0</v>
-      </c>
-      <c r="O96" s="12">
-        <f>IF((K96-J96)&lt;0,0,(K96-J96))</f>
-        <v>0</v>
-      </c>
-      <c r="P96" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q96" s="12"/>
-      <c r="R96" s="10"/>
-      <c r="S96" s="12"/>
-      <c r="T96" s="12">
-        <f>IF((P96-Q96)&lt;0,0,(P96-Q96))</f>
-        <v>0</v>
-      </c>
-      <c r="U96" s="12">
-        <f>IF((Q96-P96)&lt;0,0,(Q96-P96))</f>
-        <v>0</v>
-      </c>
-      <c r="V96" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W96" s="12"/>
-      <c r="X96" s="10"/>
-      <c r="Y96" s="12"/>
-      <c r="Z96" s="12">
-        <f>IF((V96-W96)&lt;0,0,(V96-W96))</f>
-        <v>0</v>
-      </c>
-      <c r="AA96" s="12">
-        <f>IF((W96-V96)&lt;0,0,(W96-V96))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
-      <c r="A97" s="10">
-        <v>10</v>
-      </c>
-      <c r="B97" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C97" s="10"/>
-      <c r="D97" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E97" s="12"/>
-      <c r="F97" s="10"/>
-      <c r="G97" s="12"/>
-      <c r="H97" s="12">
-        <f>IF((D97-E97)&lt;0,0,(D97-E97))</f>
-        <v>0</v>
-      </c>
-      <c r="I97" s="12">
-        <f>IF((E97-D97)&lt;0,0,(E97-D97))</f>
-        <v>0</v>
-      </c>
-      <c r="J97" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K97" s="12"/>
-      <c r="L97" s="10"/>
-      <c r="M97" s="12"/>
-      <c r="N97" s="12">
-        <f>IF((J97-K97)&lt;0,0,(J97-K97))</f>
-        <v>0</v>
-      </c>
-      <c r="O97" s="12">
-        <f>IF((K97-J97)&lt;0,0,(K97-J97))</f>
-        <v>0</v>
-      </c>
-      <c r="P97" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q97" s="12"/>
-      <c r="R97" s="10"/>
-      <c r="S97" s="12"/>
-      <c r="T97" s="12">
-        <f>IF((P97-Q97)&lt;0,0,(P97-Q97))</f>
-        <v>0</v>
-      </c>
-      <c r="U97" s="12">
-        <f>IF((Q97-P97)&lt;0,0,(Q97-P97))</f>
-        <v>0</v>
-      </c>
-      <c r="V97" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W97" s="12"/>
-      <c r="X97" s="10"/>
-      <c r="Y97" s="12"/>
-      <c r="Z97" s="12">
-        <f>IF((V97-W97)&lt;0,0,(V97-W97))</f>
-        <v>0</v>
-      </c>
-      <c r="AA97" s="12">
-        <f>IF((W97-V97)&lt;0,0,(W97-V97))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
-      <c r="A98" s="10">
-        <v>10</v>
-      </c>
-      <c r="B98" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C98" s="10"/>
-      <c r="D98" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E98" s="12"/>
-      <c r="F98" s="10"/>
-      <c r="G98" s="12"/>
-      <c r="H98" s="12">
-        <f>IF((D98-E98)&lt;0,0,(D98-E98))</f>
-        <v>0</v>
-      </c>
-      <c r="I98" s="12">
-        <f>IF((E98-D98)&lt;0,0,(E98-D98))</f>
-        <v>0</v>
-      </c>
-      <c r="J98" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K98" s="12"/>
-      <c r="L98" s="10"/>
-      <c r="M98" s="12"/>
-      <c r="N98" s="12">
-        <f>IF((J98-K98)&lt;0,0,(J98-K98))</f>
-        <v>0</v>
-      </c>
-      <c r="O98" s="12">
-        <f>IF((K98-J98)&lt;0,0,(K98-J98))</f>
-        <v>0</v>
-      </c>
-      <c r="P98" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q98" s="12"/>
-      <c r="R98" s="10"/>
-      <c r="S98" s="12"/>
-      <c r="T98" s="12">
-        <f>IF((P98-Q98)&lt;0,0,(P98-Q98))</f>
-        <v>0</v>
-      </c>
-      <c r="U98" s="12">
-        <f>IF((Q98-P98)&lt;0,0,(Q98-P98))</f>
-        <v>0</v>
-      </c>
-      <c r="V98" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W98" s="12"/>
-      <c r="X98" s="10"/>
-      <c r="Y98" s="12"/>
-      <c r="Z98" s="12">
-        <f>IF((V98-W98)&lt;0,0,(V98-W98))</f>
-        <v>0</v>
-      </c>
-      <c r="AA98" s="12">
-        <f>IF((W98-V98)&lt;0,0,(W98-V98))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
-      <c r="A99" s="10">
-        <v>10</v>
-      </c>
-      <c r="B99" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C99" s="10"/>
-      <c r="D99" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E99" s="12"/>
-      <c r="F99" s="10"/>
-      <c r="G99" s="12"/>
-      <c r="H99" s="12">
-        <f>IF((D99-E99)&lt;0,0,(D99-E99))</f>
-        <v>0</v>
-      </c>
-      <c r="I99" s="12">
-        <f>IF((E99-D99)&lt;0,0,(E99-D99))</f>
-        <v>0</v>
-      </c>
-      <c r="J99" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K99" s="12"/>
-      <c r="L99" s="10"/>
-      <c r="M99" s="12"/>
-      <c r="N99" s="12">
-        <f>IF((J99-K99)&lt;0,0,(J99-K99))</f>
-        <v>0</v>
-      </c>
-      <c r="O99" s="12">
-        <f>IF((K99-J99)&lt;0,0,(K99-J99))</f>
-        <v>0</v>
-      </c>
-      <c r="P99" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q99" s="12"/>
-      <c r="R99" s="10"/>
-      <c r="S99" s="12"/>
-      <c r="T99" s="12">
-        <f>IF((P99-Q99)&lt;0,0,(P99-Q99))</f>
-        <v>0</v>
-      </c>
-      <c r="U99" s="12">
-        <f>IF((Q99-P99)&lt;0,0,(Q99-P99))</f>
-        <v>0</v>
-      </c>
-      <c r="V99" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W99" s="12"/>
-      <c r="X99" s="10"/>
-      <c r="Y99" s="12"/>
-      <c r="Z99" s="12">
-        <f>IF((V99-W99)&lt;0,0,(V99-W99))</f>
-        <v>0</v>
-      </c>
-      <c r="AA99" s="12">
-        <f>IF((W99-V99)&lt;0,0,(W99-V99))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
-      <c r="A100" s="10">
-        <v>10</v>
-      </c>
-      <c r="B100" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C100" s="10"/>
-      <c r="D100" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E100" s="12"/>
-      <c r="F100" s="10"/>
-      <c r="G100" s="12"/>
-      <c r="H100" s="12">
-        <f>IF((D100-E100)&lt;0,0,(D100-E100))</f>
-        <v>0</v>
-      </c>
-      <c r="I100" s="12">
-        <f>IF((E100-D100)&lt;0,0,(E100-D100))</f>
-        <v>0</v>
-      </c>
-      <c r="J100" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K100" s="12"/>
-      <c r="L100" s="10"/>
-      <c r="M100" s="12"/>
-      <c r="N100" s="12">
-        <f>IF((J100-K100)&lt;0,0,(J100-K100))</f>
-        <v>0</v>
-      </c>
-      <c r="O100" s="12">
-        <f>IF((K100-J100)&lt;0,0,(K100-J100))</f>
-        <v>0</v>
-      </c>
-      <c r="P100" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q100" s="12"/>
-      <c r="R100" s="10"/>
-      <c r="S100" s="12"/>
-      <c r="T100" s="12">
-        <f>IF((P100-Q100)&lt;0,0,(P100-Q100))</f>
-        <v>0</v>
-      </c>
-      <c r="U100" s="12">
-        <f>IF((Q100-P100)&lt;0,0,(Q100-P100))</f>
-        <v>0</v>
-      </c>
-      <c r="V100" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W100" s="12"/>
-      <c r="X100" s="10"/>
-      <c r="Y100" s="12"/>
-      <c r="Z100" s="12">
-        <f>IF((V100-W100)&lt;0,0,(V100-W100))</f>
-        <v>0</v>
-      </c>
-      <c r="AA100" s="12">
-        <f>IF((W100-V100)&lt;0,0,(W100-V100))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
-      <c r="A101" s="10">
-        <v>10</v>
-      </c>
-      <c r="B101" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C101" s="10"/>
-      <c r="D101" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E101" s="12"/>
-      <c r="F101" s="10"/>
-      <c r="G101" s="12"/>
-      <c r="H101" s="12">
-        <f>IF((D101-E101)&lt;0,0,(D101-E101))</f>
-        <v>0</v>
-      </c>
-      <c r="I101" s="12">
-        <f>IF((E101-D101)&lt;0,0,(E101-D101))</f>
-        <v>0</v>
-      </c>
-      <c r="J101" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K101" s="12"/>
-      <c r="L101" s="10"/>
-      <c r="M101" s="12"/>
-      <c r="N101" s="12">
-        <f>IF((J101-K101)&lt;0,0,(J101-K101))</f>
-        <v>0</v>
-      </c>
-      <c r="O101" s="12">
-        <f>IF((K101-J101)&lt;0,0,(K101-J101))</f>
-        <v>0</v>
-      </c>
-      <c r="P101" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q101" s="12"/>
-      <c r="R101" s="10"/>
-      <c r="S101" s="12"/>
-      <c r="T101" s="12">
-        <f>IF((P101-Q101)&lt;0,0,(P101-Q101))</f>
-        <v>0</v>
-      </c>
-      <c r="U101" s="12">
-        <f>IF((Q101-P101)&lt;0,0,(Q101-P101))</f>
-        <v>0</v>
-      </c>
-      <c r="V101" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W101" s="12"/>
-      <c r="X101" s="10"/>
-      <c r="Y101" s="12"/>
-      <c r="Z101" s="12">
-        <f>IF((V101-W101)&lt;0,0,(V101-W101))</f>
-        <v>0</v>
-      </c>
-      <c r="AA101" s="12">
-        <f>IF((W101-V101)&lt;0,0,(W101-V101))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
-      <c r="J102" s="13"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="13"/>
-      <c r="O102" s="13"/>
-      <c r="P102" s="13"/>
-      <c r="S102" s="5"/>
-      <c r="T102" s="13"/>
-      <c r="U102" s="13"/>
-      <c r="V102" s="13"/>
-      <c r="Y102" s="5"/>
-      <c r="Z102" s="13"/>
-      <c r="AA102" s="13"/>
-    </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
-      <c r="A103" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C103" s="1"/>
-      <c r="D103" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E103" s="5"/>
-      <c r="F103" s="1"/>
-      <c r="G103" s="5"/>
-      <c r="H103" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I103" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J103" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K103" s="5"/>
-      <c r="L103" s="1"/>
-      <c r="M103" s="5"/>
-      <c r="N103" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O103" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P103" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q103" s="5"/>
-      <c r="R103" s="1"/>
-      <c r="S103" s="5"/>
-      <c r="T103" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U103" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V103" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W103" s="5"/>
-      <c r="X103" s="1"/>
-      <c r="Y103" s="5"/>
-      <c r="Z103" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA103" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
-      <c r="A104" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B104" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C104" s="1"/>
-      <c r="D104" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E104" s="5"/>
-      <c r="F104" s="1"/>
-      <c r="G104" s="5"/>
-      <c r="H104" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I104" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J104" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K104" s="5"/>
-      <c r="L104" s="1"/>
-      <c r="M104" s="5"/>
-      <c r="N104" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O104" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P104" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q104" s="5"/>
-      <c r="R104" s="1"/>
-      <c r="S104" s="5"/>
-      <c r="T104" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U104" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V104" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W104" s="5"/>
-      <c r="X104" s="1"/>
-      <c r="Y104" s="5"/>
-      <c r="Z104" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA104" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
-      <c r="A105" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B105" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C105" s="1"/>
-      <c r="D105" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E105" s="5"/>
-      <c r="F105" s="1"/>
-      <c r="G105" s="5"/>
-      <c r="H105" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I105" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J105" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K105" s="5"/>
-      <c r="L105" s="1"/>
-      <c r="M105" s="5"/>
-      <c r="N105" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O105" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P105" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q105" s="5"/>
-      <c r="R105" s="1"/>
-      <c r="S105" s="5"/>
-      <c r="T105" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U105" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V105" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W105" s="5"/>
-      <c r="X105" s="1"/>
-      <c r="Y105" s="5"/>
-      <c r="Z105" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA105" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
-      <c r="A106" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B106" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C106" s="1"/>
-      <c r="D106" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E106" s="5"/>
-      <c r="F106" s="1"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I106" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J106" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K106" s="5"/>
-      <c r="L106" s="1"/>
-      <c r="M106" s="5"/>
-      <c r="N106" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O106" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P106" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q106" s="5"/>
-      <c r="R106" s="1"/>
-      <c r="S106" s="5"/>
-      <c r="T106" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U106" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V106" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W106" s="5"/>
-      <c r="X106" s="1"/>
-      <c r="Y106" s="5"/>
-      <c r="Z106" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA106" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
-      <c r="A107" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B107" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C107" s="1"/>
-      <c r="D107" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E107" s="5"/>
-      <c r="F107" s="1"/>
-      <c r="G107" s="5"/>
-      <c r="H107" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I107" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J107" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K107" s="5"/>
-      <c r="L107" s="1"/>
-      <c r="M107" s="5"/>
-      <c r="N107" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O107" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P107" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q107" s="5"/>
-      <c r="R107" s="1"/>
-      <c r="S107" s="5"/>
-      <c r="T107" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U107" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V107" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W107" s="5"/>
-      <c r="X107" s="1"/>
-      <c r="Y107" s="5"/>
-      <c r="Z107" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA107" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
-      <c r="A108" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B108" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C108" s="1"/>
-      <c r="D108" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E108" s="5"/>
-      <c r="F108" s="1"/>
-      <c r="G108" s="5"/>
-      <c r="H108" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I108" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J108" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K108" s="5"/>
-      <c r="L108" s="1"/>
-      <c r="M108" s="5"/>
-      <c r="N108" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O108" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P108" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q108" s="5"/>
-      <c r="R108" s="1"/>
-      <c r="S108" s="5"/>
-      <c r="T108" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U108" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V108" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W108" s="5"/>
-      <c r="X108" s="1"/>
-      <c r="Y108" s="5"/>
-      <c r="Z108" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA108" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
-      <c r="A109" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B109" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C109" s="1"/>
-      <c r="D109" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E109" s="5"/>
-      <c r="F109" s="1"/>
-      <c r="G109" s="5"/>
-      <c r="H109" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I109" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J109" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K109" s="5"/>
-      <c r="L109" s="1"/>
-      <c r="M109" s="5"/>
-      <c r="N109" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O109" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P109" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q109" s="5"/>
-      <c r="R109" s="1"/>
-      <c r="S109" s="5"/>
-      <c r="T109" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U109" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V109" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W109" s="5"/>
-      <c r="X109" s="1"/>
-      <c r="Y109" s="5"/>
-      <c r="Z109" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA109" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
-      <c r="A110" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B110" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C110" s="1"/>
-      <c r="D110" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E110" s="5"/>
-      <c r="F110" s="1"/>
-      <c r="G110" s="5"/>
-      <c r="H110" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I110" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J110" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K110" s="5"/>
-      <c r="L110" s="1"/>
-      <c r="M110" s="5"/>
-      <c r="N110" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O110" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P110" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q110" s="5"/>
-      <c r="R110" s="1"/>
-      <c r="S110" s="5"/>
-      <c r="T110" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U110" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V110" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W110" s="5"/>
-      <c r="X110" s="1"/>
-      <c r="Y110" s="5"/>
-      <c r="Z110" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA110" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
-      <c r="J111" s="13"/>
-      <c r="N111" s="13"/>
-      <c r="O111" s="13"/>
-      <c r="P111" s="13"/>
-      <c r="T111" s="13"/>
-      <c r="U111" s="13"/>
-      <c r="V111" s="13"/>
-      <c r="Z111" s="13"/>
-      <c r="AA111" s="13"/>
-    </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
-      <c r="A112" s="1"/>
-      <c r="B112" s="9"/>
-      <c r="C112" s="1"/>
-      <c r="D112" s="5"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="1"/>
-      <c r="G112" s="5"/>
-      <c r="H112" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I112" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J112" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K112" s="5"/>
-      <c r="L112" s="1"/>
-      <c r="M112" s="5"/>
-      <c r="N112" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O112" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P112" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q112" s="5"/>
-      <c r="R112" s="1"/>
-      <c r="S112" s="5"/>
-      <c r="T112" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U112" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V112" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W112" s="5"/>
-      <c r="X112" s="1"/>
-      <c r="Y112" s="5"/>
-      <c r="Z112" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA112" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
-      <c r="A113" s="1"/>
-      <c r="B113" s="9"/>
-      <c r="C113" s="1"/>
-      <c r="D113" s="5"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="1"/>
-      <c r="G113" s="5"/>
-      <c r="H113" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I113" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J113" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K113" s="5"/>
-      <c r="L113" s="1"/>
-      <c r="M113" s="5"/>
-      <c r="N113" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O113" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P113" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q113" s="5"/>
-      <c r="R113" s="1"/>
-      <c r="S113" s="5"/>
-      <c r="T113" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U113" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V113" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W113" s="5"/>
-      <c r="X113" s="1"/>
-      <c r="Y113" s="5"/>
-      <c r="Z113" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA113" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
-      <c r="A114" s="1"/>
-      <c r="B114" s="9"/>
-      <c r="C114" s="1"/>
-      <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="1"/>
-      <c r="G114" s="5"/>
-      <c r="H114" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I114" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J114" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K114" s="5"/>
-      <c r="L114" s="1"/>
-      <c r="M114" s="5"/>
-      <c r="N114" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O114" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P114" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q114" s="5"/>
-      <c r="R114" s="1"/>
-      <c r="S114" s="5"/>
-      <c r="T114" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U114" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V114" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W114" s="5"/>
-      <c r="X114" s="1"/>
-      <c r="Y114" s="5"/>
-      <c r="Z114" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA114" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
-      <c r="A115" s="1"/>
-      <c r="B115" s="9"/>
-      <c r="C115" s="1"/>
-      <c r="D115" s="5"/>
-      <c r="E115" s="5"/>
-      <c r="F115" s="1"/>
-      <c r="G115" s="5"/>
-      <c r="H115" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I115" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J115" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K115" s="5"/>
-      <c r="L115" s="1"/>
-      <c r="M115" s="5"/>
-      <c r="N115" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O115" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P115" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q115" s="5"/>
-      <c r="R115" s="1"/>
-      <c r="S115" s="5"/>
-      <c r="T115" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U115" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V115" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W115" s="5"/>
-      <c r="X115" s="1"/>
-      <c r="Y115" s="5"/>
-      <c r="Z115" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA115" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
-      <c r="A116" s="1"/>
-      <c r="B116" s="9"/>
-      <c r="C116" s="1"/>
-      <c r="D116" s="5"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="1"/>
-      <c r="G116" s="5"/>
-      <c r="H116" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I116" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J116" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K116" s="5"/>
-      <c r="L116" s="1"/>
-      <c r="M116" s="5"/>
-      <c r="N116" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O116" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P116" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q116" s="5"/>
-      <c r="R116" s="1"/>
-      <c r="S116" s="5"/>
-      <c r="T116" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U116" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V116" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W116" s="5"/>
-      <c r="X116" s="1"/>
-      <c r="Y116" s="5"/>
-      <c r="Z116" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA116" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
-      <c r="A117" s="1"/>
-      <c r="B117" s="9"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="5"/>
-      <c r="E117" s="5"/>
-      <c r="F117" s="1"/>
-      <c r="G117" s="5"/>
-      <c r="H117" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I117" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J117" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K117" s="5"/>
-      <c r="L117" s="1"/>
-      <c r="M117" s="5"/>
-      <c r="N117" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O117" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P117" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q117" s="5"/>
-      <c r="R117" s="1"/>
-      <c r="S117" s="5"/>
-      <c r="T117" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U117" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V117" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W117" s="5"/>
-      <c r="X117" s="1"/>
-      <c r="Y117" s="5"/>
-      <c r="Z117" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA117" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
-      <c r="A118" s="1"/>
-      <c r="B118" s="9"/>
-      <c r="C118" s="1"/>
-      <c r="D118" s="5"/>
-      <c r="E118" s="5"/>
-      <c r="F118" s="1"/>
-      <c r="G118" s="5"/>
-      <c r="H118" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I118" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J118" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K118" s="5"/>
-      <c r="L118" s="1"/>
-      <c r="M118" s="5"/>
-      <c r="N118" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O118" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P118" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q118" s="5"/>
-      <c r="R118" s="1"/>
-      <c r="S118" s="5"/>
-      <c r="T118" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U118" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V118" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W118" s="5"/>
-      <c r="X118" s="1"/>
-      <c r="Y118" s="5"/>
-      <c r="Z118" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA118" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
-      <c r="A119" s="1"/>
-      <c r="B119" s="9"/>
-      <c r="C119" s="1"/>
-      <c r="D119" s="5"/>
-      <c r="E119" s="5"/>
-      <c r="F119" s="1"/>
-      <c r="G119" s="5"/>
-      <c r="H119" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I119" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J119" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K119" s="5"/>
-      <c r="L119" s="1"/>
-      <c r="M119" s="5"/>
-      <c r="N119" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O119" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P119" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q119" s="5"/>
-      <c r="R119" s="1"/>
-      <c r="S119" s="5"/>
-      <c r="T119" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U119" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V119" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W119" s="5"/>
-      <c r="X119" s="1"/>
-      <c r="Y119" s="5"/>
-      <c r="Z119" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA119" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
-      <c r="A120" s="1"/>
-      <c r="B120" s="9"/>
-      <c r="C120" s="1"/>
-      <c r="D120" s="5"/>
-      <c r="E120" s="5"/>
-      <c r="F120" s="1"/>
-      <c r="G120" s="5"/>
-      <c r="H120" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I120" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J120" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K120" s="5"/>
-      <c r="L120" s="1"/>
-      <c r="M120" s="5"/>
-      <c r="N120" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O120" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P120" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q120" s="5"/>
-      <c r="R120" s="1"/>
-      <c r="S120" s="5"/>
-      <c r="T120" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U120" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V120" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W120" s="5"/>
-      <c r="X120" s="1"/>
-      <c r="Y120" s="5"/>
-      <c r="Z120" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA120" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
-      <c r="A121" s="1"/>
-      <c r="B121" s="9"/>
-      <c r="C121" s="1"/>
-      <c r="D121" s="5"/>
-      <c r="E121" s="5"/>
-      <c r="F121" s="1"/>
-      <c r="G121" s="5"/>
-      <c r="H121" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I121" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J121" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K121" s="5"/>
-      <c r="L121" s="1"/>
-      <c r="M121" s="5"/>
-      <c r="N121" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O121" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P121" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q121" s="5"/>
-      <c r="R121" s="1"/>
-      <c r="S121" s="5"/>
-      <c r="T121" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U121" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V121" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W121" s="5"/>
-      <c r="X121" s="1"/>
-      <c r="Y121" s="5"/>
-      <c r="Z121" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA121" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
-      <c r="A122" s="1"/>
-      <c r="B122" s="9"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="5"/>
-      <c r="E122" s="5"/>
-      <c r="F122" s="1"/>
-      <c r="G122" s="5"/>
-      <c r="H122" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I122" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J122" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K122" s="5"/>
-      <c r="L122" s="1"/>
-      <c r="M122" s="5"/>
-      <c r="N122" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O122" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P122" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q122" s="5"/>
-      <c r="R122" s="1"/>
-      <c r="S122" s="5"/>
-      <c r="T122" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U122" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V122" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W122" s="5"/>
-      <c r="X122" s="1"/>
-      <c r="Y122" s="5"/>
-      <c r="Z122" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA122" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
-      <c r="A123" s="1"/>
-      <c r="B123" s="9"/>
-      <c r="C123" s="1"/>
-      <c r="D123" s="5"/>
-      <c r="E123" s="5"/>
-      <c r="F123" s="1"/>
-      <c r="G123" s="5"/>
-      <c r="H123" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I123" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J123" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K123" s="5"/>
-      <c r="L123" s="1"/>
-      <c r="M123" s="5"/>
-      <c r="N123" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O123" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P123" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q123" s="5"/>
-      <c r="R123" s="1"/>
-      <c r="S123" s="5"/>
-      <c r="T123" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U123" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V123" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W123" s="5"/>
-      <c r="X123" s="1"/>
-      <c r="Y123" s="5"/>
-      <c r="Z123" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA123" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
-      <c r="A124" s="1"/>
-      <c r="B124" s="9"/>
-      <c r="C124" s="1"/>
-      <c r="D124" s="5"/>
-      <c r="E124" s="5"/>
-      <c r="F124" s="1"/>
-      <c r="G124" s="5"/>
-      <c r="H124" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I124" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J124" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K124" s="5"/>
-      <c r="L124" s="1"/>
-      <c r="M124" s="5"/>
-      <c r="N124" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O124" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P124" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q124" s="5"/>
-      <c r="R124" s="1"/>
-      <c r="S124" s="5"/>
-      <c r="T124" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U124" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V124" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W124" s="5"/>
-      <c r="X124" s="1"/>
-      <c r="Y124" s="5"/>
-      <c r="Z124" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA124" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
-      <c r="A125" s="1"/>
-      <c r="B125" s="9"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="5"/>
-      <c r="E125" s="5"/>
-      <c r="F125" s="1"/>
-      <c r="G125" s="5"/>
-      <c r="H125" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I125" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J125" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K125" s="5"/>
-      <c r="L125" s="1"/>
-      <c r="M125" s="5"/>
-      <c r="N125" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O125" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P125" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q125" s="5"/>
-      <c r="R125" s="1"/>
-      <c r="S125" s="5"/>
-      <c r="T125" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U125" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V125" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W125" s="5"/>
-      <c r="X125" s="1"/>
-      <c r="Y125" s="5"/>
-      <c r="Z125" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA125" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
-      <c r="A126" s="1"/>
-      <c r="B126" s="9"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="5"/>
-      <c r="E126" s="5"/>
-      <c r="F126" s="1"/>
-      <c r="G126" s="5"/>
-      <c r="H126" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I126" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J126" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K126" s="5"/>
-      <c r="L126" s="1"/>
-      <c r="M126" s="5"/>
-      <c r="N126" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O126" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P126" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q126" s="5"/>
-      <c r="R126" s="1"/>
-      <c r="S126" s="5"/>
-      <c r="T126" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U126" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V126" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W126" s="5"/>
-      <c r="X126" s="1"/>
-      <c r="Y126" s="5"/>
-      <c r="Z126" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA126" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
-      <c r="A127" s="29"/>
-      <c r="B127" s="30"/>
-      <c r="C127" s="29"/>
-      <c r="D127" s="5"/>
-      <c r="E127" s="31"/>
-      <c r="F127" s="29"/>
-      <c r="G127" s="31"/>
-      <c r="H127" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I127" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J127" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K127" s="31"/>
-      <c r="L127" s="29"/>
-      <c r="M127" s="31"/>
-      <c r="N127" s="5">
-        <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
-        <v>0</v>
-      </c>
-      <c r="O127" s="5">
-        <f t="shared" ref="O127" si="25">IF((K127-J127)&lt;0,0,(K127-J127))</f>
-        <v>0</v>
-      </c>
-      <c r="P127" s="5"/>
-      <c r="Q127" s="31"/>
-      <c r="R127" s="29"/>
-      <c r="S127" s="31"/>
-      <c r="T127" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U127" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V127" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W127" s="31"/>
-      <c r="X127" s="29"/>
-      <c r="Y127" s="31"/>
-      <c r="Z127" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA127" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
+    <row r="62" spans="1:27" s="7" customFormat="1">
+      <c r="A62"/>
+      <c r="B62"/>
+      <c r="C62"/>
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="F62"/>
+      <c r="G62"/>
+      <c r="H62"/>
+      <c r="I62"/>
+      <c r="J62"/>
+      <c r="K62"/>
+      <c r="L62"/>
+      <c r="M62"/>
+      <c r="N62"/>
+      <c r="O62"/>
+      <c r="P62"/>
+      <c r="Q62"/>
+      <c r="R62"/>
+      <c r="S62"/>
+      <c r="T62"/>
+      <c r="U62"/>
+      <c r="V62"/>
+      <c r="W62"/>
+      <c r="X62"/>
+      <c r="Y62"/>
+      <c r="Z62"/>
+      <c r="AA62"/>
+    </row>
+    <row r="72" spans="1:27" s="7" customFormat="1">
+      <c r="A72"/>
+      <c r="B72"/>
+      <c r="C72"/>
+      <c r="D72"/>
+      <c r="E72"/>
+      <c r="F72"/>
+      <c r="G72"/>
+      <c r="H72"/>
+      <c r="I72"/>
+      <c r="J72"/>
+      <c r="K72"/>
+      <c r="L72"/>
+      <c r="M72"/>
+      <c r="N72"/>
+      <c r="O72"/>
+      <c r="P72"/>
+      <c r="Q72"/>
+      <c r="R72"/>
+      <c r="S72"/>
+      <c r="T72"/>
+      <c r="U72"/>
+      <c r="V72"/>
+      <c r="W72"/>
+      <c r="X72"/>
+      <c r="Y72"/>
+      <c r="Z72"/>
+      <c r="AA72"/>
+    </row>
+    <row r="82" spans="1:27" s="7" customFormat="1">
+      <c r="A82"/>
+      <c r="B82"/>
+      <c r="C82"/>
+      <c r="D82"/>
+      <c r="E82"/>
+      <c r="F82"/>
+      <c r="G82"/>
+      <c r="H82"/>
+      <c r="I82"/>
+      <c r="J82"/>
+      <c r="K82"/>
+      <c r="L82"/>
+      <c r="M82"/>
+      <c r="N82"/>
+      <c r="O82"/>
+      <c r="P82"/>
+      <c r="Q82"/>
+      <c r="R82"/>
+      <c r="S82"/>
+      <c r="T82"/>
+      <c r="U82"/>
+      <c r="V82"/>
+      <c r="W82"/>
+      <c r="X82"/>
+      <c r="Y82"/>
+      <c r="Z82"/>
+      <c r="AA82"/>
+    </row>
+    <row r="92" spans="1:27" s="7" customFormat="1">
+      <c r="A92"/>
+      <c r="B92"/>
+      <c r="C92"/>
+      <c r="D92"/>
+      <c r="E92"/>
+      <c r="F92"/>
+      <c r="G92"/>
+      <c r="H92"/>
+      <c r="I92"/>
+      <c r="J92"/>
+      <c r="K92"/>
+      <c r="L92"/>
+      <c r="M92"/>
+      <c r="N92"/>
+      <c r="O92"/>
+      <c r="P92"/>
+      <c r="Q92"/>
+      <c r="R92"/>
+      <c r="S92"/>
+      <c r="T92"/>
+      <c r="U92"/>
+      <c r="V92"/>
+      <c r="W92"/>
+      <c r="X92"/>
+      <c r="Y92"/>
+      <c r="Z92"/>
+      <c r="AA92"/>
+    </row>
+    <row r="102" spans="1:27" s="7" customFormat="1">
+      <c r="A102"/>
+      <c r="B102"/>
+      <c r="C102"/>
+      <c r="D102"/>
+      <c r="E102"/>
+      <c r="F102"/>
+      <c r="G102"/>
+      <c r="H102"/>
+      <c r="I102"/>
+      <c r="J102"/>
+      <c r="K102"/>
+      <c r="L102"/>
+      <c r="M102"/>
+      <c r="N102"/>
+      <c r="O102"/>
+      <c r="P102"/>
+      <c r="Q102"/>
+      <c r="R102"/>
+      <c r="S102"/>
+      <c r="T102"/>
+      <c r="U102"/>
+      <c r="V102"/>
+      <c r="W102"/>
+      <c r="X102"/>
+      <c r="Y102"/>
+      <c r="Z102"/>
+      <c r="AA102"/>
+    </row>
+    <row r="111" spans="1:27" s="7" customFormat="1">
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+      <c r="D111"/>
+      <c r="E111"/>
+      <c r="F111"/>
+      <c r="G111"/>
+      <c r="H111"/>
+      <c r="I111"/>
+      <c r="J111"/>
+      <c r="K111"/>
+      <c r="L111"/>
+      <c r="M111"/>
+      <c r="N111"/>
+      <c r="O111"/>
+      <c r="P111"/>
+      <c r="Q111"/>
+      <c r="R111"/>
+      <c r="S111"/>
+      <c r="T111"/>
+      <c r="U111"/>
+      <c r="V111"/>
+      <c r="W111"/>
+      <c r="X111"/>
+      <c r="Y111"/>
+      <c r="Z111"/>
+      <c r="AA111"/>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C5:C12" name="Textbooks"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 N5:R12 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 T5:X12 N4:P4 T4:V4 J4 Y13 N3:R3 K14:L21 K23:L31 N13:P61 P2:R2 V2:X3 T13:V61 J6:J61 Z4:AA61 D5:F12" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G23:G31 G33:G41 G43:G51 S4:S61 G5:G12 M5:M12 M14:M61 Y5:Y12 G14:G21 Y14:Y61 M3 G53:G61" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -13361,18 +8706,12 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
-      <formula1>"CO,RO,SDO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M61 Y14:Y61 S4:S61 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{5A3B4BE6-62D4-4D9D-A016-659A8D57B7DD}">
-      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13388,7 +8727,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
   <dimension ref="A1:AB140"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
     <col min="2" max="2" width="27.85546875" customWidth="1"/>
@@ -13416,124 +8755,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="B1" s="32"/>
+      <c r="D1" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="W1" s="42"/>
+      <c r="X1" s="42"/>
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="42"/>
+      <c r="AA1" s="42"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="33" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="16" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="M2" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="N2" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="O2" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="P2" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="Q2" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="R2" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="S2" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="T2" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="U2" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="V2" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="W2" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="X2" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="Y2" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="Z2" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="Q2" s="24" t="s">
+      <c r="AA2" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="R2" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="S2" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="T2" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U2" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="V2" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="W2" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="X2" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y2" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z2" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA2" s="26" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="19.149999999999999">
+    </row>
+    <row r="3" spans="1:27" ht="34.5">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -13602,12 +8941,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="20.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="5">
@@ -13671,12 +9010,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="20.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="5">
@@ -13740,12 +9079,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="20.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="5">
@@ -13809,12 +9148,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="20.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="5">
@@ -13878,12 +9217,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="20.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -13947,12 +9286,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="20.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -14016,12 +9355,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="20.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -14086,7 +9425,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="34.5">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14155,12 +9494,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999">
+    <row r="13" spans="1:27" ht="20.25">
       <c r="A13" s="1">
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="5">
@@ -14224,12 +9563,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="20.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="5">
@@ -14293,12 +9632,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="20.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="5">
@@ -14362,12 +9701,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="20.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="5">
@@ -14431,12 +9770,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="20.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="5">
@@ -14500,12 +9839,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="20.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="5">
@@ -14569,12 +9908,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="20.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="5">
@@ -14639,7 +9978,7 @@
       </c>
     </row>
     <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="34.5">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -14708,12 +10047,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="20.25">
       <c r="A22" s="1">
         <v>3</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="5">
@@ -14777,12 +10116,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="20.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="5">
@@ -14846,12 +10185,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="20.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -14915,12 +10254,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="20.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="5">
@@ -14984,12 +10323,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="20.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="5">
@@ -15053,12 +10392,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="20.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="5">
@@ -15122,12 +10461,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="20.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="5">
@@ -15191,12 +10530,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="20.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="5">
@@ -15261,12 +10600,12 @@
       </c>
     </row>
     <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="20.25">
       <c r="A31" s="1">
         <v>4</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -15330,12 +10669,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="20.25">
       <c r="A32" s="1">
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="5">
@@ -15399,12 +10738,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="20.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -15468,12 +10807,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="20.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -15537,12 +10876,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="20.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="5">
@@ -15606,12 +10945,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="20.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -15675,12 +11014,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
-      <c r="A37" s="37">
+    <row r="37" spans="1:27" ht="20.25">
+      <c r="A37" s="34">
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5">
@@ -15744,12 +11083,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="20.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -15813,12 +11152,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="20.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="5">
@@ -15882,12 +11221,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
-      <c r="A40" s="37">
+    <row r="40" spans="1:27" ht="20.25">
+      <c r="A40" s="34">
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5">
@@ -15951,12 +11290,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="20.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -16021,12 +11360,12 @@
       </c>
     </row>
     <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="20.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -16090,12 +11429,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="20.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -16159,12 +11498,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="20.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="5">
@@ -16228,12 +11567,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="20.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="5">
@@ -16297,12 +11636,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="20.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="5">
@@ -16366,12 +11705,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="20.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -16435,12 +11774,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
-      <c r="A49" s="37">
+    <row r="49" spans="1:27" ht="20.25">
+      <c r="A49" s="34">
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5">
@@ -16504,12 +11843,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="20.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -16573,12 +11912,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="20.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="5">
@@ -16642,12 +11981,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999">
-      <c r="A52" s="37">
+    <row r="52" spans="1:27" ht="20.25">
+      <c r="A52" s="34">
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5">
@@ -16711,12 +12050,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="20.25">
       <c r="A53" s="1">
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -16781,12 +12120,12 @@
       </c>
     </row>
     <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="20.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="5">
@@ -16850,12 +12189,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="20.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="5">
@@ -16919,12 +12258,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="20.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="5">
@@ -16988,12 +12327,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="20.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -17057,12 +12396,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="20.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="5">
@@ -17126,12 +12465,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="20.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="5">
@@ -17195,12 +12534,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
-      <c r="A61" s="37">
+    <row r="61" spans="1:27" ht="20.25">
+      <c r="A61" s="34">
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5">
@@ -17264,12 +12603,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999">
+    <row r="62" spans="1:27" ht="20.25">
       <c r="A62" s="1">
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="5">
@@ -17333,12 +12672,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="20.25">
       <c r="A63" s="1">
         <v>6</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="5">
@@ -17402,12 +12741,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
-      <c r="A64" s="37">
+    <row r="64" spans="1:27" ht="20.25">
+      <c r="A64" s="34">
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5">
@@ -17471,12 +12810,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="20.25">
       <c r="A65" s="1">
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="5">
@@ -17541,12 +12880,12 @@
       </c>
     </row>
     <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="20.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -17610,12 +12949,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="20.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -17679,12 +13018,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="20.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="12">
@@ -17748,12 +13087,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="20.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="12">
@@ -17817,12 +13156,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="20.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="12">
@@ -17886,12 +13225,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="20.25">
       <c r="A72" s="10">
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="12">
@@ -17955,12 +13294,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
-      <c r="A73" s="38">
+    <row r="73" spans="1:27" ht="20.25">
+      <c r="A73" s="35">
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="12">
@@ -18024,12 +13363,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="20.25">
       <c r="A74" s="10">
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -18093,12 +13432,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="20.25">
       <c r="A75" s="10">
         <v>7</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="12">
@@ -18162,12 +13501,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
-      <c r="A76" s="38">
+    <row r="76" spans="1:27" ht="20.25">
+      <c r="A76" s="35">
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="12">
@@ -18231,12 +13570,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="20.25">
       <c r="A77" s="10">
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -18301,12 +13640,12 @@
       </c>
     </row>
     <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="20.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -18370,12 +13709,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="20.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -18439,12 +13778,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="20.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="12">
@@ -18508,12 +13847,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="20.25">
       <c r="A82" s="10">
         <v>8</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="12">
@@ -18577,12 +13916,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="20.25">
       <c r="A83" s="10">
         <v>8</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -18646,12 +13985,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="20.25">
       <c r="A84" s="10">
         <v>8</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -18715,12 +14054,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
-      <c r="A85" s="38">
+    <row r="85" spans="1:27" ht="20.25">
+      <c r="A85" s="35">
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="12">
@@ -18784,12 +14123,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="20.25">
       <c r="A86" s="10">
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -18853,12 +14192,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="20.25">
       <c r="A87" s="10">
         <v>8</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="12">
@@ -18922,12 +14261,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
-      <c r="A88" s="38">
+    <row r="88" spans="1:27" ht="20.25">
+      <c r="A88" s="35">
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C88" s="12"/>
       <c r="D88" s="12">
@@ -18991,12 +14330,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="20.25">
       <c r="A89" s="10">
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -19061,12 +14400,12 @@
       </c>
     </row>
     <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="20.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -19130,12 +14469,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="20.25">
       <c r="A92" s="10">
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="12">
@@ -19199,12 +14538,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="20.25">
       <c r="A93" s="10">
         <v>9</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -19268,12 +14607,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="20.25">
       <c r="A94" s="10">
         <v>9</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -19337,12 +14676,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="20.25">
       <c r="A95" s="10">
         <v>9</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="12">
@@ -19406,12 +14745,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="20.25">
       <c r="A96" s="10">
         <v>9</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -19475,12 +14814,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
-      <c r="A97" s="38">
+    <row r="97" spans="1:27" ht="20.25">
+      <c r="A97" s="35">
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -19544,12 +14883,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="20.25">
       <c r="A98" s="10">
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -19613,12 +14952,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="20.25">
       <c r="A99" s="10">
         <v>9</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="12">
@@ -19682,12 +15021,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
-      <c r="A100" s="38">
+    <row r="100" spans="1:27" ht="20.25">
+      <c r="A100" s="35">
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -19751,12 +15090,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="20.25">
       <c r="A101" s="10">
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -19821,12 +15160,12 @@
       </c>
     </row>
     <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="103" spans="1:27" ht="20.25">
       <c r="A103" s="10">
         <v>10</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="12">
@@ -19890,12 +15229,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="20.25">
       <c r="A104" s="10">
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="12">
@@ -19959,12 +15298,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="20.25">
       <c r="A105" s="10">
         <v>10</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="12">
@@ -20028,12 +15367,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="20.25">
       <c r="A106" s="10">
         <v>10</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="12">
@@ -20097,12 +15436,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="20.25">
       <c r="A107" s="10">
         <v>10</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="12">
@@ -20166,12 +15505,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="20.25">
       <c r="A108" s="10">
         <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="12">
@@ -20235,12 +15574,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
-      <c r="A109" s="38">
+    <row r="109" spans="1:27" ht="20.25">
+      <c r="A109" s="35">
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="12">
@@ -20304,12 +15643,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="20.25">
       <c r="A110" s="10">
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="12">
@@ -20373,12 +15712,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="20.25">
       <c r="A111" s="10">
         <v>10</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="12">
@@ -20442,12 +15781,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
-      <c r="A112" s="38">
+    <row r="112" spans="1:27" ht="20.25">
+      <c r="A112" s="35">
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="12">
@@ -20511,12 +15850,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="20.25">
       <c r="A113" s="10">
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="12">
@@ -20581,12 +15920,12 @@
       </c>
     </row>
     <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="115" spans="1:28" ht="34.5">
       <c r="A115" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="5">
@@ -20650,12 +15989,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="20.25">
       <c r="A116" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="5">
@@ -20719,12 +16058,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="20.25">
       <c r="A117" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="5">
@@ -20788,12 +16127,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="20.25">
       <c r="A118" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="5">
@@ -20857,12 +16196,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="34.5">
       <c r="A119" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="5">
@@ -20926,12 +16265,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="34.5">
       <c r="A120" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="5">
@@ -20995,12 +16334,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="34.5">
       <c r="A121" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="5">
@@ -21064,12 +16403,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="34.5">
       <c r="A122" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="5">
@@ -21657,14 +16996,11 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025 ,2026"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{5FBE900B-01BC-494C-BA1B-4E6B9CEA0AA3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
